--- a/docs/mbs/inputs/columbia-mo-2026-05-08/tiktok.xlsx
+++ b/docs/mbs/inputs/columbia-mo-2026-05-08/tiktok.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
   <si>
     <t>Ad name</t>
   </si>
@@ -64,6 +64,9 @@
     <t>Secondary status</t>
   </si>
   <si>
+    <t>Campaign paused; Ad group paused; Ad completed</t>
+  </si>
+  <si>
     <t>Ad group paused; Ad completed</t>
   </si>
   <si>
@@ -337,13 +340,13 @@
     <t>Result rate</t>
   </si>
   <si>
-    <t>Deep funnel result</t>
-  </si>
-  <si>
-    <t>Cost per deep funnel result</t>
-  </si>
-  <si>
-    <t>Deep funnel result rate</t>
+    <t>Qualified conversion</t>
+  </si>
+  <si>
+    <t>Cost per qualified conversion</t>
+  </si>
+  <si>
+    <t>Qualified conversion rate</t>
   </si>
   <si>
     <t>Secondary source</t>
@@ -720,82 +723,82 @@
         <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2">
@@ -809,22 +812,22 @@
         <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J2" s="2">
         <v>3331</v>
@@ -842,10 +845,10 @@
         <v>0</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q2" s="3">
         <v>0.0000</v>
@@ -860,7 +863,7 @@
         <v>13</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V2" s="3">
         <v>0.0039</v>
@@ -875,16 +878,16 @@
         <v>14</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AB2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3">
@@ -898,22 +901,22 @@
         <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J3" s="2">
         <v>6249</v>
@@ -931,10 +934,10 @@
         <v>0</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="3">
         <v>0.0000</v>
@@ -949,7 +952,7 @@
         <v>25</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V3" s="3">
         <v>0.0040</v>
@@ -964,16 +967,16 @@
         <v>14</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AB3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4">
@@ -987,22 +990,22 @@
         <v>16</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J4" s="2">
         <v>6163</v>
@@ -1020,10 +1023,10 @@
         <v>0</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q4" s="3">
         <v>0.0000</v>
@@ -1038,7 +1041,7 @@
         <v>39</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V4" s="3">
         <v>0.0063</v>
@@ -1053,16 +1056,16 @@
         <v>14</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AB4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5">
@@ -1076,22 +1079,22 @@
         <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J5" s="2">
         <v>4530</v>
@@ -1109,10 +1112,10 @@
         <v>0</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q5" s="3">
         <v>0.0000</v>
@@ -1127,7 +1130,7 @@
         <v>19</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V5" s="3">
         <v>0.0042</v>
@@ -1142,16 +1145,16 @@
         <v>14</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AB5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6">
@@ -1165,22 +1168,22 @@
         <v>16</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J6" s="2">
         <v>4334</v>
@@ -1198,10 +1201,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q6" s="3">
         <v>0.0000</v>
@@ -1216,7 +1219,7 @@
         <v>17</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V6" s="3">
         <v>0.0039</v>
@@ -1231,16 +1234,16 @@
         <v>14</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AB6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7">
@@ -1254,22 +1257,22 @@
         <v>16</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="2">
         <v>62655</v>
@@ -1287,10 +1290,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q7" s="3">
         <v>0.0000</v>
@@ -1305,7 +1308,7 @@
         <v>345</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V7" s="3">
         <v>0.0055</v>
@@ -1320,16 +1323,16 @@
         <v>14</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8">
@@ -1343,22 +1346,22 @@
         <v>16</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J8" s="2">
         <v>55982</v>
@@ -1376,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q8" s="3">
         <v>0.0000</v>
@@ -1394,7 +1397,7 @@
         <v>256</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="V8" s="3">
         <v>0.0046</v>
@@ -1409,16 +1412,16 @@
         <v>14</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AB8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9">
@@ -1432,22 +1435,22 @@
         <v>16</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J9" s="2">
         <v>79255</v>
@@ -1465,10 +1468,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q9" s="3">
         <v>0.0000</v>
@@ -1483,7 +1486,7 @@
         <v>456</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V9" s="3">
         <v>0.0058</v>
@@ -1498,16 +1501,16 @@
         <v>14</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AB9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10">
@@ -1521,22 +1524,22 @@
         <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J10" s="2">
         <v>87138</v>
@@ -1554,10 +1557,10 @@
         <v>0</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q10" s="3">
         <v>0.0000</v>
@@ -1572,7 +1575,7 @@
         <v>470</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V10" s="3">
         <v>0.0054</v>
@@ -1587,16 +1590,16 @@
         <v>14</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AB10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AC10" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">
@@ -1610,22 +1613,22 @@
         <v>16</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J11" s="2">
         <v>37695</v>
@@ -1643,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q11" s="3">
         <v>0.0000</v>
@@ -1661,7 +1664,7 @@
         <v>160</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V11" s="3">
         <v>0.0042</v>
@@ -1676,16 +1679,16 @@
         <v>14</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AB11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12">
@@ -1696,25 +1699,25 @@
         <v>13</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J12" s="2">
         <v>18322</v>
@@ -1732,10 +1735,10 @@
         <v>36</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q12" s="3">
         <v>0.2250</v>
@@ -1750,7 +1753,7 @@
         <v>36</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="V12" s="3">
         <v>0.0020</v>
@@ -1765,16 +1768,16 @@
         <v>14</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AB12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13">
@@ -1785,25 +1788,25 @@
         <v>13</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J13" s="2">
         <v>29759</v>
@@ -1821,10 +1824,10 @@
         <v>61</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q13" s="3">
         <v>0.2542</v>
@@ -1839,7 +1842,7 @@
         <v>61</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V13" s="3">
         <v>0.0020</v>
@@ -1854,16 +1857,16 @@
         <v>14</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AB13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -1874,25 +1877,25 @@
         <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J14" s="2">
         <v>7914</v>
@@ -1910,10 +1913,10 @@
         <v>10</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q14" s="3">
         <v>0.2564</v>
@@ -1928,7 +1931,7 @@
         <v>10</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="V14" s="3">
         <v>0.0013</v>
@@ -1943,16 +1946,16 @@
         <v>14</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA14" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AB14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15">
@@ -1963,25 +1966,25 @@
         <v>13</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J15" s="2">
         <v>11579</v>
@@ -1999,10 +2002,10 @@
         <v>11</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q15" s="3">
         <v>0.1642</v>
@@ -2017,7 +2020,7 @@
         <v>11</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="V15" s="3">
         <v>0.0009</v>
@@ -2032,16 +2035,16 @@
         <v>14</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA15" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AB15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AC15" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16">
@@ -2052,25 +2055,25 @@
         <v>13</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J16" s="2">
         <v>9818</v>
@@ -2088,10 +2091,10 @@
         <v>7</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q16" s="3">
         <v>0.1373</v>
@@ -2106,7 +2109,7 @@
         <v>7</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="V16" s="3">
         <v>0.0007</v>
@@ -2121,16 +2124,16 @@
         <v>14</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AB16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17">
@@ -2153,13 +2156,13 @@
         <v>14</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J17" s="2">
         <v>424724</v>
@@ -2177,7 +2180,7 @@
         <v>14</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>14</v>
@@ -2219,7 +2222,7 @@
         <v>14</v>
       </c>
       <c r="AC17" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
